--- a/data/trans_orig/ProbViv_estruc-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22071</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47837</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52054</t>
+          <t>52129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>77959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96553</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29409</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>52708</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60417</t>
+          <t>61086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106264</t>
+          <t>104013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408246</t>
+          <t>407802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431101</t>
+          <t>430608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456202</t>
+          <t>455533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480050</t>
+          <t>479311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870865</t>
+          <t>873116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>904866</t>
+          <t>905837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19108</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>31501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129444</t>
+          <t>130470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141012</t>
+          <t>141540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164787</t>
+          <t>164764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176928</t>
+          <t>176528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299108</t>
+          <t>299456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314970</t>
+          <t>315850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51732</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82928</t>
+          <t>83043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118573</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161934</t>
+          <t>162192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>580811</t>
+          <t>580696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612007</t>
+          <t>612268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672046</t>
+          <t>670525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701525</t>
+          <t>702998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1262833</t>
+          <t>1262575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1306194</t>
+          <t>1307069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_estruc-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_estruc-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14035</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19949</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12650</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7039</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42697</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36783</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42028</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31755</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47639</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>29478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52129</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>78630</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77959</t>
+          <t>70329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>85527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>44380</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34081</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57085</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40181</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29902</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>52708</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>38574</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>30459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61086</t>
+          <t>48790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>68806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104013</t>
+          <t>98082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>431298</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>418593</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>441597</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>581</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>420329</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>407802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>430608</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>469283</t>
+          <t>393874</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455533</t>
+          <t>383658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479311</t>
+          <t>401989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>889612</t>
+          <t>825173</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>873116</t>
+          <t>810044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>905837</t>
+          <t>839320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9769</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5282</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16583</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11975</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7012</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18082</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31501</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157693</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150879</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>162180</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>136577</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130470</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141540</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>171987</t>
+          <t>136944</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164764</t>
+          <t>130507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176528</t>
+          <t>141559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>308565</t>
+          <t>294636</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>299456</t>
+          <t>285273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315850</t>
+          <t>301161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68184</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54905</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83074</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>64805</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51471</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>49590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>75846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129539</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117698</t>
+          <t>113405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162192</t>
+          <t>148609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>631688</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>616798</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>644967</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>847</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>598934</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>580696</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>612268</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>687699</t>
+          <t>566750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670525</t>
+          <t>552260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702998</t>
+          <t>578516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1286632</t>
+          <t>1198439</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1262575</t>
+          <t>1179369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1307069</t>
+          <t>1214573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
